--- a/antibodies/latest/antibodies.xlsx
+++ b/antibodies/latest/antibodies.xlsx
@@ -22,10 +22,12 @@
   <commentList>
     <comment ref="A1" authorId="1">
       <text>
-        <t>(Required) Structure of the identifier depends on the acquisition system.
-Whenever possible this should exactly match the channel ID in the OME TIFF file.
-For example the channel ID in an OME TIFF might be something like "Channel:0:13"
-which would then be the value entered here.</t>
+        <t>The identifier of the imaging channel as recorded by the acquisition system.
+This identifier typically refers to a specific biological structure or marker
+imaged (e.g., nucleus, cell membrane) and should exactly match the channel ID
+present in the metadata of the OME-TIFF file. For instance, if the channel ID in
+an OME TIFF is "Channel:0:13", this exact value should be entered here. Example:
+Channel:0:13</t>
       </text>
     </comment>
     <comment ref="B1" authorId="1">
@@ -68,8 +70,8 @@
     </comment>
     <comment ref="H1" authorId="1">
       <text>
-        <t>The concentration units of the antibody preparation. Leave blank if not
-applicable.</t>
+        <t>The unit of measurement for the antibody concentration value. If the
+concentration is not applicable, this field may be left blank. Example: ug/ml</t>
       </text>
     </comment>
     <comment ref="I1" authorId="1">
@@ -86,8 +88,8 @@
     </comment>
     <comment ref="K1" authorId="1">
       <text>
-        <t>(Required) The string that serves as the definitive identifier for the metadata
-schema version and is readily interpretable by computers for data validation and
+        <t>(Required) The unique string identifier for the metadata specification version,
+which is easily interpretable by computers for purposes of data validation and
 processing. Example: 22bc762a-5020-419d-b170-24253ed9e8d9</t>
       </text>
     </comment>
@@ -155,7 +157,7 @@
     <t>pav:createdOn</t>
   </si>
   <si>
-    <t>2025-03-14T19:47:05-04:00</t>
+    <t>2026-10-21T13:28:21-07:00</t>
   </si>
   <si>
     <t>pav:derivedFrom</t>
